--- a/real_data/cp_test_random_seeds_2para_20k.xlsx
+++ b/real_data/cp_test_random_seeds_2para_20k.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BNU\BA4\毕业论文\LTRC-changepoint\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CFDB43-37AF-45C7-9B5A-AC7436EA97C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BAE305-B109-4DB7-95A3-B441DAC8E576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="2210" windowWidth="13450" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-460" yWindow="2290" windowWidth="13450" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
